--- a/reference/七阶段开发任务清单.xlsx
+++ b/reference/七阶段开发任务清单.xlsx
@@ -470,7 +470,7 @@
         <x:v>目标</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
-        <x:v>Win7 RTM x86/x64 纯净 VM 通过 L3</x:v>
+        <x:v>Win7 SP1 x86/x64 纯净 VM 通过 L3</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
         <x:v>周期</x:v>
@@ -642,7 +642,7 @@
         <x:v>环境与 VM 基线</x:v>
       </x:c>
       <x:c r="E11" s="8" t="str">
-        <x:v>安装 VS2017 v141_xp、CMake 3.15、XMake 2.9.x；创建 Win7 RTM 6.1.7600 x86、x64 VirtualBox VM；确认无 SP1、无 VC++ 运行库、无 Office，并建立 00_Base。</x:v>
+        <x:v>安装 VS2017 v141_xp、CMake 3.15、XMake 2.9.x；创建 Win7 SP1 6.1.7601 x86、x64 VirtualBox VM；确认 SP1 基线、无 VC++ 运行库、无 Office，并建立 00_Base。</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
         <x:v>构建环境记录、CMake/XMake 版本记录、两台 VM 版本截图、00_Base 快照名、脱敏样表传入路径。</x:v>
@@ -785,7 +785,7 @@
         <x:v>建立 CMakeLists.txt（正式）与 xmake.lua（辅助镜像），均锁定 Win32 Release、C++14、MSVC2017 v141_xp、Unicode、/MT、0x0601；分别执行构建/测试，候选包仅由 CMake install 生成。</x:v>
       </x:c>
       <x:c r="F15" s="18" t="str">
-        <x:v>CMake/XMake 命令与配置对照、32 位 CMake 候选 exe、依赖检查、两台 Win7 RTM VM 启动证据。</x:v>
+        <x:v>CMake/XMake 命令与配置对照、32 位 CMake 候选 exe、依赖检查、两台 Win7 SP1 VM 启动证据。</x:v>
       </x:c>
       <x:c r="G15" s="18" t="str">
         <x:v>R 在 x86/x64 VM 仅复核 CMake 候选包。</x:v>
@@ -1360,7 +1360,7 @@
         <x:v>□</x:v>
       </x:c>
       <x:c r="K31" s="18" t="str">
-        <x:v>L3：Win7 RTM x86/x64</x:v>
+        <x:v>L3：Win7 SP1 x86/x64</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="92" customHeight="1">
@@ -1720,7 +1720,7 @@
         <x:v>字段字典、页面流程、00_Base、接口/风险登记已评审</x:v>
       </x:c>
       <x:c r="E6" s="8" t="str">
-        <x:v>两台 VM 基线；无 SP1/Office/VC++ 运行库</x:v>
+        <x:v>两台 VM 基线；SP1 6.1.7601；无 Office/VC++ 运行库</x:v>
       </x:c>
       <x:c r="F6" s="19" t="str">
         <x:v>□ 通过  □ 阻断</x:v>
@@ -1737,7 +1737,7 @@
         <x:v>C++14 工程、目录、公共接口、空 UI</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
-        <x:v>Win32 Release 空程序在 Win7 RTM x86/x64 均启动；接口 v1 冻结</x:v>
+        <x:v>Win32 Release 空程序在 Win7 SP1 x86/x64 均启动；接口 v1 冻结</x:v>
       </x:c>
       <x:c r="E7" s="8" t="str">
         <x:v>L1 两台 VM 启动与依赖检查</x:v>
@@ -1911,7 +1911,7 @@
         <x:v>L2</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
-        <x:v>Win7 RTM VM</x:v>
+        <x:v>Win7 SP1 VM</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
         <x:v>功能、中文路径、无 Office、导出/打印</x:v>
@@ -1931,7 +1931,7 @@
         <x:v>L3</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
-        <x:v>00_Base 恢复后的 Win7 RTM x86/x64 VM</x:v>
+        <x:v>00_Base 恢复后的 Win7 SP1 x86/x64 VM</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
         <x:v>纯净部署、首次启动到恢复全流程</x:v>
@@ -2245,7 +2245,7 @@
         <x:v>D6</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>Win7 RTM x86/x64 L3</x:v>
+        <x:v>Win7 SP1 x86/x64 L3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
